--- a/BOM_主板.xlsx
+++ b/BOM_主板.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_Board1_PCB1_2026-07-14" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_Board1_Schematic1_2026-07-2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="258">
   <si>
     <t>No.</t>
   </si>
@@ -46,22 +46,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>2.7kHz</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>BUZ-TH_BD9.6-P5.00-D0.7-FD</t>
-  </si>
-  <si>
-    <t>TMB9650-DC5V-DF</t>
-  </si>
-  <si>
-    <t>XHXDZ(兴华鑫)</t>
-  </si>
-  <si>
-    <t>C50387088</t>
+    <t>2.4kHz</t>
+  </si>
+  <si>
+    <t>BUZZER1</t>
+  </si>
+  <si>
+    <t>BUZ-TH_BD12.0-P7.60-D0.6-FD</t>
+  </si>
+  <si>
+    <t>TMB12A05</t>
+  </si>
+  <si>
+    <t>华能</t>
+  </si>
+  <si>
+    <t>C96093</t>
   </si>
   <si>
     <t>LCSC</t>
@@ -76,16 +76,16 @@
     <t>C1,C3,C18,C20</t>
   </si>
   <si>
-    <t>CAP-SMD_L3.2-W1.6-FD</t>
-  </si>
-  <si>
-    <t>CA55-A016M106T</t>
-  </si>
-  <si>
-    <t>湘怡中元/湘江</t>
-  </si>
-  <si>
-    <t>C568915</t>
+    <t>CAP-SMD_L3.2-W1.6-RD-C7171</t>
+  </si>
+  <si>
+    <t>TAJA106K016RNJ</t>
+  </si>
+  <si>
+    <t>Kyocera AVX</t>
+  </si>
+  <si>
+    <t>C7171</t>
   </si>
   <si>
     <t>3</t>
@@ -94,12 +94,114 @@
     <t>100nF</t>
   </si>
   <si>
-    <t>C2,C4,C5,C13,C16,C19,C21,C23,C25</t>
+    <t>C2,C4,C19,C21</t>
   </si>
   <si>
     <t>C0603</t>
   </si>
   <si>
+    <t>CGA0603X7R104K500JT</t>
+  </si>
+  <si>
+    <t>HRE(芯声)</t>
+  </si>
+  <si>
+    <t>C6119867</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>C5,C13,C16,C23,C25</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>47uF</t>
+  </si>
+  <si>
+    <t>C6,C17</t>
+  </si>
+  <si>
+    <t>C1206</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>C7,C22</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD6.3-P2.50-D0.5-FD</t>
+  </si>
+  <si>
+    <t>ERG25V220M6X11</t>
+  </si>
+  <si>
+    <t>JIERR(捷而瑞)</t>
+  </si>
+  <si>
+    <t>C47344177</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>C12,C24</t>
+  </si>
+  <si>
+    <t>C3216X7R1V475M085AC</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>C5610230</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>C14,C26</t>
+  </si>
+  <si>
+    <t>CAP-TH_BD8.0-P3.50-D0.5-FD</t>
+  </si>
+  <si>
+    <t>ERG50V100M8X12</t>
+  </si>
+  <si>
+    <t>C47344183</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>4.7nF</t>
+  </si>
+  <si>
+    <t>C15,C27</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
     <t>CL10B104KB8NNNC</t>
   </si>
   <si>
@@ -109,115 +211,7 @@
     <t>C1591</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>47uF</t>
-  </si>
-  <si>
-    <t>C6,C17</t>
-  </si>
-  <si>
-    <t>C1206</t>
-  </si>
-  <si>
-    <t>HGC1206R5476M250NSPJ</t>
-  </si>
-  <si>
-    <t>Chinocera(华瓷)</t>
-  </si>
-  <si>
-    <t>C22367835</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>220uF</t>
-  </si>
-  <si>
-    <t>C7,C22</t>
-  </si>
-  <si>
-    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.3-FD-H7.7</t>
-  </si>
-  <si>
-    <t>JVJ25V220M6x8</t>
-  </si>
-  <si>
-    <t>JIERR(捷而瑞)</t>
-  </si>
-  <si>
-    <t>C46550404</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>C12,C24</t>
-  </si>
-  <si>
-    <t>CGA1206X5R475K350NT</t>
-  </si>
-  <si>
-    <t>HRE(芯声)</t>
-  </si>
-  <si>
-    <t>C22399656</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>100uF</t>
-  </si>
-  <si>
-    <t>C14,C26</t>
-  </si>
-  <si>
-    <t>CAP-SMD_BD6.3-L6.6-W6.6-RD</t>
-  </si>
-  <si>
-    <t>MA35V100M6X8</t>
-  </si>
-  <si>
-    <t>C46550467</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4.7nF</t>
-  </si>
-  <si>
-    <t>C15,C27</t>
-  </si>
-  <si>
-    <t>CL10B472KB8NNNC</t>
-  </si>
-  <si>
-    <t>C1621</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
-    <t>YAGEO(国巨)</t>
-  </si>
-  <si>
-    <t>C14663</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>BZT52C16</t>
@@ -229,16 +223,13 @@
     <t>SOD-123_L2.7-W1.6-LS3.7-RD</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>R+O(宏嘉诚)</t>
-  </si>
-  <si>
-    <t>C19077413</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>Slkor(萨科微)</t>
+  </si>
+  <si>
+    <t>C707145</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>SS54</t>
@@ -247,16 +238,19 @@
     <t>D2,D3</t>
   </si>
   <si>
-    <t>SMA_L4.3-W2.6-LS5.0-FD</t>
-  </si>
-  <si>
-    <t>C7420369</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>B5819WS</t>
+    <t>SMA_L4.4-W2.8-LS5.4-R-RD</t>
+  </si>
+  <si>
+    <t>MDD(辰达半导体)</t>
+  </si>
+  <si>
+    <t>C22452</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>B5819WS-TP</t>
   </si>
   <si>
     <t>D4</t>
@@ -265,673 +259,532 @@
     <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
   </si>
   <si>
-    <t>C499641</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>DB301V-3.5-2P-GN-S</t>
-  </si>
-  <si>
-    <t>DCOUT1,DCOUT2</t>
-  </si>
-  <si>
-    <t>CONN-TH_DB301V-3.5-2P-GN</t>
-  </si>
-  <si>
-    <t>DORABO(地博电气)</t>
-  </si>
-  <si>
-    <t>C695629</t>
+    <t>MCC(美微科)</t>
+  </si>
+  <si>
+    <t>C78734</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>HDR-M_2.54_2x3</t>
+  </si>
+  <si>
+    <t>H8,H9,P8</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-R2-C3-S2.54_A2541WV-2X3P</t>
+  </si>
+  <si>
+    <t>C402781</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>4.7uH</t>
   </si>
   <si>
-    <t>L1,L2</t>
-  </si>
-  <si>
-    <t>IND-SMD_L5.4-W5.2_FXL0530</t>
-  </si>
-  <si>
-    <t>FXL0530-4R7-M</t>
-  </si>
-  <si>
-    <t>cjiang(长江微电)</t>
-  </si>
-  <si>
-    <t>C177246</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>GL0603UR01</t>
-  </si>
-  <si>
-    <t>LED1,LED3,LED4,LED5,LED6</t>
-  </si>
-  <si>
-    <t>LED0603-FD</t>
-  </si>
-  <si>
-    <t>Guiguang light(桂光光电)</t>
-  </si>
-  <si>
-    <t>C51933292</t>
+    <t>L,L2</t>
+  </si>
+  <si>
+    <t>IND-SMD_L7.2-W6.6_GPSR07X0</t>
+  </si>
+  <si>
+    <t>CYA0630-4.7UH</t>
+  </si>
+  <si>
+    <t>SHOU HAN(首韩)</t>
+  </si>
+  <si>
+    <t>C5189748</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>MountHole</t>
-  </si>
-  <si>
-    <t>M1,M2,M3,M4,M5,M6,M7,M8</t>
-  </si>
-  <si>
-    <t>SMD_BD4.0-L4.0-W4.0-D2.3</t>
-  </si>
-  <si>
-    <t>C9900010428</t>
+    <t>LED_0805-G</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>LED_0805</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
-    <t>2.54-2*20</t>
-  </si>
-  <si>
-    <t>P0.1,P0.3</t>
-  </si>
-  <si>
-    <t>HDR-TH_40P-P2.54-V-F-R2-C20-S2.54</t>
-  </si>
-  <si>
-    <t>ZHOURI(洲日)</t>
-  </si>
-  <si>
-    <t>C2977589</t>
+    <t>LED_0603-G</t>
+  </si>
+  <si>
+    <t>LED2,LED3,LED4,LED6</t>
+  </si>
+  <si>
+    <t>LED_0603</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>PM254-2-14-Z-8.5</t>
-  </si>
-  <si>
-    <t>P0.2</t>
-  </si>
-  <si>
-    <t>HDR-TH_28P-P2.54-V-F-R2-C14-S2.54-1</t>
-  </si>
-  <si>
-    <t>HCTL(华灿天禄)</t>
-  </si>
-  <si>
-    <t>C2897415</t>
+    <t>XT60-M.</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>CONN-TH_XT60</t>
+  </si>
+  <si>
+    <t>AMASS(艾迈斯)</t>
+  </si>
+  <si>
+    <t>C98733</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>XT60-M.</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>CONN-TH_XT60</t>
-  </si>
-  <si>
-    <t>AMASS(艾迈斯)</t>
-  </si>
-  <si>
-    <t>C98733</t>
+    <t>HDR-M_2.54_1x3P</t>
+  </si>
+  <si>
+    <t>P2,P10,P13,P14</t>
+  </si>
+  <si>
+    <t>HDR-TH_3P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>C2937625</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>PZ254V-11-03P</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>HDR-TH_3P-P2.54-V-M_PZ254V-11-03P</t>
-  </si>
-  <si>
-    <t>XFCN(兴飞)</t>
-  </si>
-  <si>
-    <t>C2937625</t>
+    <t>HDR-F_2.54_1x6P</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-F</t>
+  </si>
+  <si>
+    <t>C40877</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>Header-D-M 1x6P</t>
-  </si>
-  <si>
-    <t>P3,P9,P15.1,P15.2</t>
-  </si>
-  <si>
-    <t>HDR-TH_6P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>hanxia(韩下)</t>
-  </si>
-  <si>
-    <t>C32713272</t>
+    <t>HDR-F_2.54_1x8P</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>HDR-TH_8P-P2.54-V-F-1</t>
+  </si>
+  <si>
+    <t>C27438</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>Header-D-F 1x8P</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>HDR-TH_8P-P2.54-V-F</t>
-  </si>
-  <si>
-    <t>XKB Connection(中国星坤)</t>
-  </si>
-  <si>
-    <t>C718237</t>
+    <t>KF301-2P接线端子</t>
+  </si>
+  <si>
+    <t>P5,P6</t>
+  </si>
+  <si>
+    <t>CONN-TH_XY301V-A-5.0-2P</t>
+  </si>
+  <si>
+    <t>C9900016950</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>A254UP-ZS03P</t>
-  </si>
-  <si>
-    <t>P5,P6,P8</t>
-  </si>
-  <si>
-    <t>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54-2</t>
-  </si>
-  <si>
-    <t>BXCONN(宝讯)</t>
-  </si>
-  <si>
-    <t>C41413840</t>
+    <t>HDR-F_2.54_2x8</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>HDR-TH_16P-P2.54-V-F-R2-C8-S2.54-1</t>
+  </si>
+  <si>
+    <t>C30734</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>2.54-2*8P母</t>
-  </si>
-  <si>
-    <t>P7</t>
-  </si>
-  <si>
-    <t>HDR-TH_16P-P2.54-V-F-R2-C8-S2.54</t>
-  </si>
-  <si>
-    <t>BOOMELE(博穆精密)</t>
-  </si>
-  <si>
-    <t>C30734</t>
+    <t>HDR-M_2.54_1x6P</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-M-1</t>
+  </si>
+  <si>
+    <t>C37208</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>Header-D-M 1x3P</t>
-  </si>
-  <si>
-    <t>P10,P13,P14</t>
-  </si>
-  <si>
-    <t>CONN-TH_HX-PZ2.54-1X3P-ZZ</t>
-  </si>
-  <si>
-    <t>C32713269</t>
+    <t>HDR-F_2.54_2x4</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>HDR-TH_8P-P2.54-V-F-R2-C4-S2.54-1</t>
+  </si>
+  <si>
+    <t>C92271</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>Header-D-F 2x4P</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>HDR-TH_8P-P2.54-V-F-R2-C4-S2.54</t>
-  </si>
-  <si>
-    <t>CONNFLY</t>
-  </si>
-  <si>
-    <t>C92271</t>
+    <t>HDR-M_2.54_1x4P</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>HDR-TH_4P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>C492403</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>Header-D-M 1x4P</t>
-  </si>
-  <si>
-    <t>P12</t>
-  </si>
-  <si>
-    <t>HDR-TH_4P-P2.54-V-M-1</t>
-  </si>
-  <si>
-    <t>C5116483</t>
+    <t>HY19P03D</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>TO-252-2_L6.6-W6.1-P4.57-LS9.9-TL-CW</t>
+  </si>
+  <si>
+    <t>HUAYI(华羿微)</t>
+  </si>
+  <si>
+    <t>C122492</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>HY19P03D</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>TO-252-2_L6.6-W6.1-P4.57-LS9.9-TL-CW</t>
-  </si>
-  <si>
-    <t>HUAYI(华羿微)</t>
-  </si>
-  <si>
-    <t>C122492</t>
+    <t>MMS8050-H-TP</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>C668971</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>S8050(0.5A)</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
-  </si>
-  <si>
-    <t>EIC</t>
-  </si>
-  <si>
-    <t>C3014350</t>
+    <t>2.7K</t>
+  </si>
+  <si>
+    <t>R1,R11</t>
+  </si>
+  <si>
+    <t>R0603</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>2.7kΩ</t>
-  </si>
-  <si>
-    <t>R1,R11</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>RC0603FR-072K7L</t>
-  </si>
-  <si>
-    <t>C114612</t>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>R2,R5,R18,R25,R42</t>
   </si>
   <si>
     <t>31</t>
   </si>
   <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>RT0603BRD0710KL</t>
-  </si>
-  <si>
-    <t>C95204</t>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>R3,R41,R43</t>
   </si>
   <si>
     <t>32</t>
   </si>
   <si>
-    <t>100Ω</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>RC0603FR-07100RL</t>
-  </si>
-  <si>
-    <t>C105588</t>
+    <t>27K</t>
+  </si>
+  <si>
+    <t>R4</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>27kΩ</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>0603WAF2702T5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C22967</t>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>R6,R28,R30,R45</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
-    <t>R5,R18</t>
-  </si>
-  <si>
-    <t>FRC0603F1002TS</t>
-  </si>
-  <si>
-    <t>FOJAN(富捷)</t>
-  </si>
-  <si>
-    <t>C2906982</t>
+    <t>200K</t>
+  </si>
+  <si>
+    <t>R8,R17,R26</t>
   </si>
   <si>
     <t>35</t>
   </si>
   <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>R6,R28,R30,R34,R45</t>
-  </si>
-  <si>
-    <t>0603WAF1005T5E</t>
+    <t>8.2K</t>
+  </si>
+  <si>
+    <t>R9</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>50kΩ</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>RES-ADJ-TH_3P-L9.5-W4.85-P2.50-BL-BS</t>
-  </si>
-  <si>
-    <t>3296W-1-503</t>
-  </si>
-  <si>
-    <t>C48997928</t>
+    <t>20K</t>
+  </si>
+  <si>
+    <t>R10,R19</t>
   </si>
   <si>
     <t>37</t>
   </si>
   <si>
-    <t>200kΩ</t>
-  </si>
-  <si>
-    <t>R8,R17</t>
-  </si>
-  <si>
-    <t>0603WAF2003T5E</t>
-  </si>
-  <si>
-    <t>C25811</t>
+    <t>51K</t>
+  </si>
+  <si>
+    <t>R12</t>
   </si>
   <si>
     <t>38</t>
   </si>
   <si>
-    <t>8.2kΩ</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>0603WAF8201T5E</t>
-  </si>
-  <si>
-    <t>C25981</t>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>R13,R14,R16,R48</t>
   </si>
   <si>
     <t>39</t>
   </si>
   <si>
-    <t>20kΩ</t>
-  </si>
-  <si>
-    <t>R10,R19</t>
-  </si>
-  <si>
-    <t>FRC0603F2002TS</t>
-  </si>
-  <si>
-    <t>C2907011</t>
+    <t>1.5K</t>
+  </si>
+  <si>
+    <t>R15</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>51kΩ</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>0603WAF5102T5E</t>
-  </si>
-  <si>
-    <t>C23196</t>
+    <t>R20,R21,R22,R23</t>
+  </si>
+  <si>
+    <t>R0805</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>4.7kΩ</t>
-  </si>
-  <si>
-    <t>R13,R14,R16</t>
-  </si>
-  <si>
-    <t>RC0603FR-074K7L</t>
-  </si>
-  <si>
-    <t>C99782</t>
+    <t>1.2K</t>
+  </si>
+  <si>
+    <t>R24,R29,R44,R46</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>1.5kΩ</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>FRC0603J152 TS</t>
-  </si>
-  <si>
-    <t>C2907083</t>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>R27</t>
   </si>
   <si>
     <t>43</t>
   </si>
   <si>
-    <t>100R</t>
-  </si>
-  <si>
-    <t>R20,R21,R22,R23,R41,R43</t>
+    <t>R31,R32,R35,R37,R39</t>
   </si>
   <si>
     <t>44</t>
   </si>
   <si>
-    <t>1.2K</t>
-  </si>
-  <si>
-    <t>R24,R29,R44,R46</t>
+    <t>470R</t>
+  </si>
+  <si>
+    <t>R33,R36,R38,R40</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>20K</t>
-  </si>
-  <si>
-    <t>R25</t>
+    <t>R34</t>
   </si>
   <si>
     <t>46</t>
   </si>
   <si>
-    <t>200K</t>
-  </si>
-  <si>
-    <t>R26</t>
+    <t>47K</t>
+  </si>
+  <si>
+    <t>R47</t>
   </si>
   <si>
     <t>47</t>
   </si>
   <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>R27</t>
+    <t>50K</t>
+  </si>
+  <si>
+    <t>R49</t>
+  </si>
+  <si>
+    <t>RES-ADJ-TH_3296W</t>
+  </si>
+  <si>
+    <t>3296W-1-103</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>R31,R32,R35,R37,R39,R48</t>
+    <t>SS12D10G5</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>SW-TH_SHOU-HAN_SS12D10G4</t>
+  </si>
+  <si>
+    <t>C7431054</t>
   </si>
   <si>
     <t>49</t>
   </si>
   <si>
-    <t>470R</t>
-  </si>
-  <si>
-    <t>R33,R36,R38,R40</t>
+    <t>M3螺丝</t>
+  </si>
+  <si>
+    <t>SCREW1,SCREW2,SCREW3,SCREW4,SCREW5,SCREW6,SCREW7,SCREW8</t>
   </si>
   <si>
     <t>50</t>
   </si>
   <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R42</t>
+    <t>TS-1199A-C-B</t>
+  </si>
+  <si>
+    <t>SW2,SW3,SW4,SW5</t>
+  </si>
+  <si>
+    <t>KEY-SMD_2P-L6.0-W6.0-P6.50</t>
+  </si>
+  <si>
+    <t>XKB Connectivity(中国星坤)</t>
+  </si>
+  <si>
+    <t>C318880</t>
   </si>
   <si>
     <t>51</t>
   </si>
   <si>
-    <t>47K</t>
-  </si>
-  <si>
-    <t>R47</t>
+    <t>LS2K0300_CoreBoard</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>LS2K0300_COREBOARD</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
-    <t>SS12D10G5</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>SW-TH_SHOU-HAN_SS12D10G4</t>
-  </si>
-  <si>
-    <t>SHOU HAN(首韩)</t>
-  </si>
-  <si>
-    <t>C7431054</t>
+    <t>RT9013-33GB</t>
+  </si>
+  <si>
+    <t>U2,U5</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>RICHTEK(立锜)</t>
+  </si>
+  <si>
+    <t>C47773</t>
   </si>
   <si>
     <t>53</t>
   </si>
   <si>
-    <t>TS-1199A-B1-A</t>
-  </si>
-  <si>
-    <t>S3,S4,S5,S6</t>
-  </si>
-  <si>
-    <t>SW-SMD_L6.0-W6.0-LS6.6</t>
-  </si>
-  <si>
-    <t>C381095</t>
+    <t>运放模块</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>运放</t>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>RT9013-33GB</t>
-  </si>
-  <si>
-    <t>U2,U5</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>RICHTEK(立锜)</t>
-  </si>
-  <si>
-    <t>C47773</t>
+    <t>SCT2450CQSTER</t>
+  </si>
+  <si>
+    <t>U4,U7</t>
+  </si>
+  <si>
+    <t>ESOP-8_L4.9-W3.9-P1.27-LS6.0-BL-EP</t>
+  </si>
+  <si>
+    <t>C48971626</t>
   </si>
   <si>
     <t>55</t>
   </si>
   <si>
-    <t>SCT2450STER</t>
-  </si>
-  <si>
-    <t>U4,U7</t>
-  </si>
-  <si>
-    <t>ESOP-8_L4.9-W3.9-P1.27-LS6.0-BL-EP</t>
-  </si>
-  <si>
-    <t>SCT(芯洲科技)</t>
-  </si>
-  <si>
-    <t>C509400</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>SY6280AAC</t>
+    <t>SY6280AAAC</t>
   </si>
   <si>
     <t>U6</t>
   </si>
   <si>
+    <t>TSOT-23-5_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
     <t>Silergy(矽力杰)</t>
   </si>
   <si>
-    <t>C55136</t>
+    <t>C207620</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -1415,7 +1268,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -1447,92 +1300,92 @@
         <v>32</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I6" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J6" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -1540,31 +1393,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -1572,31 +1425,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -1604,63 +1457,63 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1668,31 +1521,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I12" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
@@ -1700,31 +1553,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -1732,31 +1585,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1764,63 +1617,63 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
@@ -1828,95 +1681,95 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H19" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="I19" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
@@ -1924,127 +1777,127 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>128</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G22" t="s">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
@@ -2052,159 +1905,159 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="E24" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G24" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>149</v>
+        <v>34</v>
       </c>
       <c r="I24" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="E25" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G25" t="s">
-        <v>152</v>
+        <v>34</v>
       </c>
       <c r="H25" t="s">
-        <v>155</v>
+        <v>34</v>
       </c>
       <c r="I25" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D26" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E27" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G27" t="s">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="J27" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B28">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G28" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="I28" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
@@ -2212,31 +2065,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B29">
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="F29" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="H29" t="s">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
@@ -2244,607 +2097,607 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F30" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="G30" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="H30" t="s">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="E31" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F31" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="G31" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="H31" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="D32" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F32" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="G32" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="H32" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I32" t="s">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="D33" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="E33" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F33" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="G33" t="s">
-        <v>199</v>
+        <v>34</v>
       </c>
       <c r="H33" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I33" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="E34" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F34" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="G34" t="s">
-        <v>204</v>
+        <v>34</v>
       </c>
       <c r="H34" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I34" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F35" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="G35" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
       <c r="H35" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="I35" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F36" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="G36" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H36" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="F37" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="G37" t="s">
-        <v>220</v>
+        <v>34</v>
       </c>
       <c r="H37" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>221</v>
+        <v>34</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>186</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="E38" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F38" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="G38" t="s">
-        <v>225</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I38" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>227</v>
+        <v>189</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>229</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F39" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="G39" t="s">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I39" t="s">
-        <v>231</v>
+        <v>34</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D40" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="E40" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="G40" t="s">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="H40" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>236</v>
+        <v>34</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C41" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="E41" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F41" t="s">
-        <v>238</v>
+        <v>169</v>
       </c>
       <c r="G41" t="s">
-        <v>240</v>
+        <v>34</v>
       </c>
       <c r="H41" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I41" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="J41" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="E42" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F42" t="s">
-        <v>243</v>
+        <v>199</v>
       </c>
       <c r="G42" t="s">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="H42" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="I42" t="s">
-        <v>246</v>
+        <v>34</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="E43" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F43" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="G43" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="H43" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="I43" t="s">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="J43" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="D44" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E44" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F44" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="G44" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H44" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="D45" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="E45" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F45" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="G45" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H45" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I45" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J45" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="E46" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F46" t="s">
-        <v>259</v>
+        <v>175</v>
       </c>
       <c r="G46" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H46" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I46" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="E47" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="F47" t="s">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="G47" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H47" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I47" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="B48">
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="D48" t="s">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="E48" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="F48" t="s">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="G48" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H48" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
       <c r="I48" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J48" t="s">
         <v>17</v>
@@ -2852,31 +2705,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="D49" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="E49" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="F49" t="s">
-        <v>268</v>
+        <v>34</v>
       </c>
       <c r="G49" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H49" t="s">
-        <v>205</v>
+        <v>94</v>
       </c>
       <c r="I49" t="s">
-        <v>72</v>
+        <v>223</v>
       </c>
       <c r="J49" t="s">
         <v>17</v>
@@ -2884,63 +2737,63 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="D50" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="E50" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="F50" t="s">
-        <v>271</v>
+        <v>34</v>
       </c>
       <c r="G50" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H50" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I50" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J50" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="D51" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="E51" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
       <c r="F51" t="s">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="G51" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="H51" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="I51" t="s">
-        <v>72</v>
+        <v>232</v>
       </c>
       <c r="J51" t="s">
         <v>17</v>
@@ -2948,63 +2801,63 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>233</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
       <c r="D52" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="E52" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="F52" t="s">
-        <v>277</v>
+        <v>34</v>
       </c>
       <c r="G52" t="s">
-        <v>215</v>
+        <v>34</v>
       </c>
       <c r="H52" t="s">
-        <v>205</v>
+        <v>34</v>
       </c>
       <c r="I52" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="D53" t="s">
-        <v>281</v>
+        <v>239</v>
       </c>
       <c r="E53" t="s">
-        <v>282</v>
+        <v>240</v>
       </c>
       <c r="F53" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G53" t="s">
-        <v>280</v>
+        <v>238</v>
       </c>
       <c r="H53" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="I53" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="J53" t="s">
         <v>17</v>
@@ -3012,63 +2865,63 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="D54" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
       <c r="E54" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="F54" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G54" t="s">
-        <v>286</v>
+        <v>34</v>
       </c>
       <c r="H54" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="I54" t="s">
-        <v>289</v>
+        <v>34</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="B55">
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="D55" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
       <c r="E55" t="s">
-        <v>293</v>
+        <v>250</v>
       </c>
       <c r="F55" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G55" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="H55" t="s">
-        <v>294</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="J55" t="s">
         <v>17</v>
@@ -3076,71 +2929,39 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="D56" t="s">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="F56" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="G56" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="H56" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="I56" t="s">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="J56" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>302</v>
-      </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
-        <v>303</v>
-      </c>
-      <c r="D57" t="s">
-        <v>304</v>
-      </c>
-      <c r="E57" t="s">
-        <v>293</v>
-      </c>
-      <c r="F57" t="s">
-        <v>72</v>
-      </c>
-      <c r="G57" t="s">
-        <v>303</v>
-      </c>
-      <c r="H57" t="s">
-        <v>305</v>
-      </c>
-      <c r="I57" t="s">
-        <v>306</v>
-      </c>
-      <c r="J57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
